--- a/data/trans_orig/Q4505_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4505_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93150</t>
+          <t>93276</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132914</t>
+          <t>131781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47998</t>
+          <t>48514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76195</t>
+          <t>77078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151516</t>
+          <t>150503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199146</t>
+          <t>197210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110948</t>
+          <t>110016</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149699</t>
+          <t>147340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66055</t>
+          <t>64647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96647</t>
+          <t>94594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184211</t>
+          <t>185543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233646</t>
+          <t>233440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>167282</t>
+          <t>165351</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209764</t>
+          <t>206343</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117212</t>
+          <t>117239</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149685</t>
+          <t>149366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>291474</t>
+          <t>289708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>348094</t>
+          <t>346972</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>33188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>25271</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50334</t>
+          <t>50128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38821</t>
+          <t>38591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>23046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>29173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55153</t>
+          <t>55748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71665</t>
+          <t>72426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104271</t>
+          <t>106365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58614</t>
+          <t>59282</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89921</t>
+          <t>89555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139384</t>
+          <t>139998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186168</t>
+          <t>185184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70682</t>
+          <t>70451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103817</t>
+          <t>103556</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>71618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103189</t>
+          <t>102889</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>149859</t>
+          <t>152371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198668</t>
+          <t>198440</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135966</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173772</t>
+          <t>173197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133333</t>
+          <t>132384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>171046</t>
+          <t>170305</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>279856</t>
+          <t>276455</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330724</t>
+          <t>332218</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43356</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,47 +1803,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>43962</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>30598</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>58029</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>11,73%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>43962</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>31684</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>57852</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36104</t>
+          <t>35542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37296</t>
+          <t>38012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68663</t>
+          <t>65366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101878</t>
+          <t>98498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139771</t>
+          <t>139530</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>37254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60113</t>
+          <t>59436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146797</t>
+          <t>147897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194699</t>
+          <t>193732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134798</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178452</t>
+          <t>178535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25448</t>
+          <t>24975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47525</t>
+          <t>46178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>167580</t>
+          <t>168147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216146</t>
+          <t>216584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>158132</t>
+          <t>158558</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>203116</t>
+          <t>200660</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56323</t>
+          <t>56797</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82496</t>
+          <t>80988</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>223281</t>
+          <t>221464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274349</t>
+          <t>274883</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26035</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51907</t>
+          <t>51396</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>32144</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60809</t>
+          <t>59376</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38226</t>
+          <t>37805</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66004</t>
+          <t>66442</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>45792</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74602</t>
+          <t>76229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>253533</t>
+          <t>254865</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>311789</t>
+          <t>311831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>157841</t>
+          <t>156190</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>202579</t>
+          <t>203203</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>426322</t>
+          <t>422997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>498788</t>
+          <t>497638</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>274153</t>
+          <t>272647</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>336336</t>
+          <t>336192</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>175767</t>
+          <t>172578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>223064</t>
+          <t>221495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>464127</t>
+          <t>464580</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>540615</t>
+          <t>541891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>445309</t>
+          <t>445644</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>516711</t>
+          <t>514112</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>219459</t>
+          <t>218243</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>270332</t>
+          <t>269849</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>681103</t>
+          <t>682268</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>768449</t>
+          <t>771323</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48891</t>
+          <t>48524</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77830</t>
+          <t>79559</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>28546</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53551</t>
+          <t>52557</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83149</t>
+          <t>81309</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>122270</t>
+          <t>121445</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89810</t>
+          <t>91280</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132397</t>
+          <t>131162</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>37974</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66011</t>
+          <t>66486</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137805</t>
+          <t>136652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>186924</t>
+          <t>188195</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70535</t>
+          <t>70467</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>103180</t>
+          <t>103358</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132436</t>
+          <t>133105</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>177155</t>
+          <t>176097</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>211647</t>
+          <t>215295</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>266478</t>
+          <t>270642</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>56854</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>87532</t>
+          <t>87776</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111368</t>
+          <t>111561</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>151335</t>
+          <t>152418</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>177630</t>
+          <t>176964</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>231064</t>
+          <t>228345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>116505</t>
+          <t>118185</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>154481</t>
+          <t>153931</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>170368</t>
+          <t>171419</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>216881</t>
+          <t>217340</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>297704</t>
+          <t>299576</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>359171</t>
+          <t>358537</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>26048</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27051</t>
+          <t>26994</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>50250</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40776</t>
+          <t>40503</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>69450</t>
+          <t>71241</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29944</t>
+          <t>30996</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54572</t>
+          <t>55222</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39055</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>67872</t>
+          <t>67466</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>75834</t>
+          <t>73891</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>112149</t>
+          <t>111664</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>269303</t>
+          <t>271890</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>331081</t>
+          <t>328815</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>301525</t>
+          <t>299293</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>366634</t>
+          <t>366004</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>59986</t>
+          <t>58490</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>88309</t>
+          <t>88099</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>247129</t>
+          <t>243907</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>302673</t>
+          <t>304608</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>316991</t>
+          <t>316055</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>381207</t>
+          <t>378779</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>133331</t>
+          <t>132717</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>168295</t>
+          <t>167993</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>479787</t>
+          <t>479241</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>550574</t>
+          <t>547655</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>623324</t>
+          <t>628454</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>706451</t>
+          <t>707928</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26898</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>41405</t>
+          <t>40260</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>68353</t>
+          <t>67930</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>56138</t>
+          <t>53461</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>86047</t>
+          <t>87649</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>32619</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>85688</t>
+          <t>85198</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>123685</t>
+          <t>122706</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>106546</t>
+          <t>106401</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>148434</t>
+          <t>150807</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>673795</t>
+          <t>672235</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>774672</t>
+          <t>771845</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>765354</t>
+          <t>767907</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>862375</t>
+          <t>868693</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1469252</t>
+          <t>1473206</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1609896</t>
+          <t>1611563</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>771787</t>
+          <t>769542</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>871210</t>
+          <t>866021</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>757069</t>
+          <t>758059</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>858314</t>
+          <t>859354</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1558754</t>
+          <t>1554648</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1699018</t>
+          <t>1696945</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1233310</t>
+          <t>1226084</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1347909</t>
+          <t>1343172</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1250249</t>
+          <t>1248233</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1364002</t>
+          <t>1365813</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2521319</t>
+          <t>2517302</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2677175</t>
+          <t>2674391</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>142628</t>
+          <t>143120</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>194440</t>
+          <t>194406</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>157099</t>
+          <t>159847</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>210822</t>
+          <t>214927</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>314248</t>
+          <t>314501</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>390804</t>
+          <t>386247</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>242750</t>
+          <t>245078</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>307968</t>
+          <t>307287</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>227552</t>
+          <t>228366</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>289928</t>
+          <t>287789</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>485506</t>
+          <t>483368</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>576933</t>
+          <t>575459</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>143039</t>
+          <t>143444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185538</t>
+          <t>187131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97298</t>
+          <t>97803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134085</t>
+          <t>133777</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249942</t>
+          <t>248855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303280</t>
+          <t>304791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122819</t>
+          <t>123914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164396</t>
+          <t>165409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,82 +5868,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>37,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>111048</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>92818</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>128339</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>35,74%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>29,88%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>41,31%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>253544</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>226040</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>281214</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>33,9%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>30,22%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>37,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>111048</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>93856</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>129755</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,74%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>253544</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>228340</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>281025</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>33,9%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65119</t>
+          <t>64940</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100084</t>
+          <t>100170</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40193</t>
+          <t>39366</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69394</t>
+          <t>67252</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114048</t>
+          <t>113389</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158044</t>
+          <t>158504</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>21375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>18741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>39632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24571</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48628</t>
+          <t>50884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28863</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40119</t>
+          <t>39671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71992</t>
+          <t>71814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105221</t>
+          <t>105295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144525</t>
+          <t>144289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100236</t>
+          <t>98482</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136153</t>
+          <t>137367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213559</t>
+          <t>210174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>269148</t>
+          <t>264459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135174</t>
+          <t>134047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>177943</t>
+          <t>176375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94769</t>
+          <t>95362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130322</t>
+          <t>130738</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240950</t>
+          <t>239491</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295174</t>
+          <t>296188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75151</t>
+          <t>75463</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>110651</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58444</t>
+          <t>60030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93332</t>
+          <t>91949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144755</t>
+          <t>144766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>193124</t>
+          <t>192924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>22635</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35327</t>
+          <t>32979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49809</t>
+          <t>49007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35304</t>
+          <t>34356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44965</t>
+          <t>44355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76387</t>
+          <t>75061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>212567</t>
+          <t>209344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>262585</t>
+          <t>260912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94797</t>
+          <t>92425</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125809</t>
+          <t>126810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>316450</t>
+          <t>316625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>374429</t>
+          <t>374819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177600</t>
+          <t>177037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>225147</t>
+          <t>224230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57625</t>
+          <t>58154</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86277</t>
+          <t>87472</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>243401</t>
+          <t>247284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301859</t>
+          <t>301325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97053</t>
+          <t>96368</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134229</t>
+          <t>134183</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53983</t>
+          <t>53825</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134168</t>
+          <t>132977</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>178811</t>
+          <t>176638</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12252</t>
+          <t>12626</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31886</t>
+          <t>32012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49566</t>
+          <t>51754</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84019</t>
+          <t>85505</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41829</t>
+          <t>41122</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79113</t>
+          <t>77568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118259</t>
+          <t>116040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>378186</t>
+          <t>377806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>446381</t>
+          <t>444382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255147</t>
+          <t>255613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310703</t>
+          <t>310470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>648650</t>
+          <t>649188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>732945</t>
+          <t>740222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>338449</t>
+          <t>335781</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>403316</t>
+          <t>400649</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>227091</t>
+          <t>226610</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>280847</t>
+          <t>282025</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>579586</t>
+          <t>581484</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>665297</t>
+          <t>665010</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>178728</t>
+          <t>179711</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>234973</t>
+          <t>234620</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>130323</t>
+          <t>131946</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>175590</t>
+          <t>178260</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>318660</t>
+          <t>322681</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>388134</t>
+          <t>392246</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45370</t>
+          <t>45810</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22080</t>
+          <t>21216</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33242</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115823</t>
+          <t>118001</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>163374</t>
+          <t>164936</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51358</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>83882</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>176283</t>
+          <t>178913</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>233461</t>
+          <t>232425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153938</t>
+          <t>156053</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>199220</t>
+          <t>198205</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>270709</t>
+          <t>273551</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>325916</t>
+          <t>327235</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>439818</t>
+          <t>439549</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>509473</t>
+          <t>508318</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>131926</t>
+          <t>131348</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>174964</t>
+          <t>174430</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>181748</t>
+          <t>181693</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>232858</t>
+          <t>233388</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>328322</t>
+          <t>327790</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>394747</t>
+          <t>392191</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71767</t>
+          <t>73316</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107611</t>
+          <t>107853</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>86939</t>
+          <t>87006</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>125748</t>
+          <t>126660</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>167926</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>218365</t>
+          <t>219591</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>14498</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>29309</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39549</t>
+          <t>39213</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>69740</t>
+          <t>70355</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>105811</t>
+          <t>107311</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>105772</t>
+          <t>106992</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>148058</t>
+          <t>149289</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>189183</t>
+          <t>189028</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>242812</t>
+          <t>242878</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>58489</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>86644</t>
+          <t>88358</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>470214</t>
+          <t>470443</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>537484</t>
+          <t>535195</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>539081</t>
+          <t>541757</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>612678</t>
+          <t>616981</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>89055</t>
+          <t>89591</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>119688</t>
+          <t>119945</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>277952</t>
+          <t>277142</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>340094</t>
+          <t>337343</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>377122</t>
+          <t>377764</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>447992</t>
+          <t>446227</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>46061</t>
+          <t>47521</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74354</t>
+          <t>73838</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>153522</t>
+          <t>151710</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>202262</t>
+          <t>201264</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>210772</t>
+          <t>211229</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>266907</t>
+          <t>266612</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>41765</t>
+          <t>40448</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25943</t>
+          <t>26812</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>49923</t>
+          <t>50473</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>30892</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>68299</t>
+          <t>71034</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>106161</t>
+          <t>106076</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>88635</t>
+          <t>85829</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>130751</t>
+          <t>127410</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1120988</t>
+          <t>1122633</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1237872</t>
+          <t>1242160</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1365869</t>
+          <t>1367083</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1489798</t>
+          <t>1487064</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2525006</t>
+          <t>2513014</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2694057</t>
+          <t>2690393</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1068581</t>
+          <t>1070400</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1182460</t>
+          <t>1177267</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1009151</t>
+          <t>1003976</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1118013</t>
+          <t>1112458</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2110318</t>
+          <t>2103213</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2263179</t>
+          <t>2261242</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>596503</t>
+          <t>596104</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>688983</t>
+          <t>690124</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>554341</t>
+          <t>557358</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>649395</t>
+          <t>648582</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1175378</t>
+          <t>1174756</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1305624</t>
+          <t>1303695</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>70374</t>
+          <t>69072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>107383</t>
+          <t>107731</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>73903</t>
+          <t>74526</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>111727</t>
+          <t>114313</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>153168</t>
+          <t>154294</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>206850</t>
+          <t>208227</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>342468</t>
+          <t>343768</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>426924</t>
+          <t>425703</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>314066</t>
+          <t>321578</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>390801</t>
+          <t>394684</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>683199</t>
+          <t>687773</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>791157</t>
+          <t>793574</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123658</t>
+          <t>126638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163429</t>
+          <t>168281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111864</t>
+          <t>112088</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148196</t>
+          <t>146960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247914</t>
+          <t>247902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>302276</t>
+          <t>302346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144607</t>
+          <t>143382</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186294</t>
+          <t>186064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120462</t>
+          <t>119133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158266</t>
+          <t>154891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275955</t>
+          <t>274944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>330929</t>
+          <t>329610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58893</t>
+          <t>59754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92200</t>
+          <t>93067</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47902</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74727</t>
+          <t>76668</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114905</t>
+          <t>115338</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160050</t>
+          <t>157332</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>20806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28309</t>
+          <t>27256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>22368</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44710</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24641</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33290</t>
+          <t>33659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60463</t>
+          <t>61007</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119426</t>
+          <t>120099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159925</t>
+          <t>159610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106187</t>
+          <t>105868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143261</t>
+          <t>143913</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236361</t>
+          <t>235453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290453</t>
+          <t>286233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123249</t>
+          <t>123833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164449</t>
+          <t>162721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122431</t>
+          <t>120144</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161401</t>
+          <t>158433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253655</t>
+          <t>258237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308360</t>
+          <t>309964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>50574</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79090</t>
+          <t>81063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55141</t>
+          <t>57229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86523</t>
+          <t>90220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>114566</t>
+          <t>115567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156888</t>
+          <t>159173</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28064</t>
+          <t>28057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>16072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36660</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>29555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53741</t>
+          <t>52880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157076</t>
+          <t>160820</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202845</t>
+          <t>202126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49421</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75058</t>
+          <t>73062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216361</t>
+          <t>215980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265896</t>
+          <t>266063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171624</t>
+          <t>170799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214673</t>
+          <t>216401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53065</t>
+          <t>53244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79598</t>
+          <t>77910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230614</t>
+          <t>235004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284115</t>
+          <t>284149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75872</t>
+          <t>78102</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110838</t>
+          <t>113485</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39941</t>
+          <t>40344</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>104896</t>
+          <t>105472</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>144832</t>
+          <t>143486</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29161</t>
+          <t>30271</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54283</t>
+          <t>54965</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64859</t>
+          <t>62379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>354318</t>
+          <t>352420</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>416922</t>
+          <t>415315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>227738</t>
+          <t>229474</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>282967</t>
+          <t>280683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>598752</t>
+          <t>599455</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>679371</t>
+          <t>681091</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>367902</t>
+          <t>368649</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>435680</t>
+          <t>437291</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>285295</t>
+          <t>283487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>341845</t>
+          <t>339083</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>669768</t>
+          <t>671489</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>752877</t>
+          <t>751845</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>193068</t>
+          <t>194151</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>248598</t>
+          <t>248282</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155873</t>
+          <t>156950</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>203606</t>
+          <t>202909</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>365144</t>
+          <t>367108</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>437381</t>
+          <t>435896</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41176</t>
+          <t>38736</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>34031</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61310</t>
+          <t>61256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89556</t>
+          <t>90526</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130458</t>
+          <t>128815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44051</t>
+          <t>44768</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75007</t>
+          <t>77030</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>145363</t>
+          <t>143812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>195209</t>
+          <t>195478</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162971</t>
+          <t>165817</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>209324</t>
+          <t>211548</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>243694</t>
+          <t>244837</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>298204</t>
+          <t>296936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>424201</t>
+          <t>424722</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>499636</t>
+          <t>494089</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>192518</t>
+          <t>191198</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>238266</t>
+          <t>237874</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>231472</t>
+          <t>231540</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>280490</t>
+          <t>283001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>437176</t>
+          <t>436615</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>506139</t>
+          <t>507843</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97369</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>138639</t>
+          <t>138116</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>110817</t>
+          <t>114399</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151862</t>
+          <t>155467</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>222928</t>
+          <t>224114</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>278885</t>
+          <t>280505</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19595</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>42234</t>
+          <t>41055</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64222</t>
+          <t>65971</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>97835</t>
+          <t>98125</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>53220</t>
+          <t>54721</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86381</t>
+          <t>87959</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>127045</t>
+          <t>128891</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>175233</t>
+          <t>176841</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71200</t>
+          <t>71595</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>102620</t>
+          <t>103079</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>341448</t>
+          <t>339501</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>409296</t>
+          <t>406607</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>423197</t>
+          <t>426021</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>498119</t>
+          <t>496648</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>85111</t>
+          <t>83614</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>117599</t>
+          <t>114861</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>342003</t>
+          <t>343559</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>405577</t>
+          <t>405007</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>438201</t>
+          <t>438454</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>510802</t>
+          <t>506982</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>54308</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84464</t>
+          <t>84339</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>155083</t>
+          <t>157168</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>203613</t>
+          <t>206716</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>221534</t>
+          <t>220404</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>278694</t>
+          <t>281259</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>20282</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>26317</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>40432</t>
+          <t>41269</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>111863</t>
+          <t>109349</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>158072</t>
+          <t>156267</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>128211</t>
+          <t>129943</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>176527</t>
+          <t>180089</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1067322</t>
+          <t>1068920</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1175273</t>
+          <t>1176444</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1151238</t>
+          <t>1156137</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1271425</t>
+          <t>1276539</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2253076</t>
+          <t>2251359</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2418944</t>
+          <t>2417747</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1160214</t>
+          <t>1161035</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1278935</t>
+          <t>1276651</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1226808</t>
+          <t>1232823</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1341328</t>
+          <t>1341693</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2418290</t>
+          <t>2418013</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2583956</t>
+          <t>2581141</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>598628</t>
+          <t>598284</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>692401</t>
+          <t>685740</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>603373</t>
+          <t>605972</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>697638</t>
+          <t>698472</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1223900</t>
+          <t>1225053</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1357494</t>
+          <t>1360631</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>75235</t>
+          <t>73547</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>112702</t>
+          <t>110450</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>54751</t>
+          <t>54807</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>87836</t>
+          <t>87317</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>136540</t>
+          <t>137707</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>188855</t>
+          <t>187047</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>268864</t>
+          <t>269409</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>335893</t>
+          <t>335794</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>268785</t>
+          <t>267491</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>338671</t>
+          <t>339714</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>555149</t>
+          <t>558003</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>649422</t>
+          <t>653886</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4505_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q4505_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93276</t>
+          <t>92795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131781</t>
+          <t>130162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48514</t>
+          <t>48058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77078</t>
+          <t>76615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150503</t>
+          <t>151490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>197210</t>
+          <t>198577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110016</t>
+          <t>107949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147340</t>
+          <t>146675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64647</t>
+          <t>65575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94594</t>
+          <t>96789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185543</t>
+          <t>183315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233440</t>
+          <t>234995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165351</t>
+          <t>167100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206343</t>
+          <t>209214</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117239</t>
+          <t>114557</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149366</t>
+          <t>149734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>289708</t>
+          <t>292227</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>346972</t>
+          <t>347900</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33188</t>
+          <t>31289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>26704</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50128</t>
+          <t>49348</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>38832</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29173</t>
+          <t>28884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55748</t>
+          <t>56015</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72426</t>
+          <t>72736</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106365</t>
+          <t>105979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59282</t>
+          <t>57265</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89555</t>
+          <t>87861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139998</t>
+          <t>139750</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185184</t>
+          <t>186299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>71361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103556</t>
+          <t>106032</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71618</t>
+          <t>70986</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102889</t>
+          <t>104556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152371</t>
+          <t>149951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>196043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135152</t>
+          <t>135865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173197</t>
+          <t>174282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132384</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>170305</t>
+          <t>169939</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>276455</t>
+          <t>278385</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332218</t>
+          <t>332094</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23974</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21263</t>
+          <t>22255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>44758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>32156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58029</t>
+          <t>57757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35542</t>
+          <t>34504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38012</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65366</t>
+          <t>67022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98498</t>
+          <t>102684</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139530</t>
+          <t>141615</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59436</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147897</t>
+          <t>146306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>193732</t>
+          <t>189475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135152</t>
+          <t>133799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178535</t>
+          <t>176249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24975</t>
+          <t>25050</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46178</t>
+          <t>46763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168147</t>
+          <t>168937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216584</t>
+          <t>216241</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>158558</t>
+          <t>157366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>200660</t>
+          <t>200073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56797</t>
+          <t>56698</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80988</t>
+          <t>82886</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>221464</t>
+          <t>220796</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274883</t>
+          <t>271323</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,26%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51396</t>
+          <t>50990</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32144</t>
+          <t>32259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59376</t>
+          <t>59642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37805</t>
+          <t>37333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66442</t>
+          <t>64153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45792</t>
+          <t>44023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76229</t>
+          <t>76442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>254865</t>
+          <t>252377</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>311831</t>
+          <t>311944</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>156190</t>
+          <t>157997</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203203</t>
+          <t>204055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>422997</t>
+          <t>422056</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>497638</t>
+          <t>499657</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>272647</t>
+          <t>275706</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>336192</t>
+          <t>335368</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>172578</t>
+          <t>176226</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>221495</t>
+          <t>225515</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>464580</t>
+          <t>465175</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>541891</t>
+          <t>539761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>445644</t>
+          <t>445548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>514112</t>
+          <t>514846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>218243</t>
+          <t>221083</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>269849</t>
+          <t>269812</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>682268</t>
+          <t>678910</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>771323</t>
+          <t>767024</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48524</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79559</t>
+          <t>78342</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>27605</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52557</t>
+          <t>51364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81309</t>
+          <t>83345</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121445</t>
+          <t>123798</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>91280</t>
+          <t>92223</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131162</t>
+          <t>132932</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>37735</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66486</t>
+          <t>65538</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136652</t>
+          <t>136777</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>188195</t>
+          <t>187037</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70467</t>
+          <t>69415</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>103358</t>
+          <t>102344</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>133105</t>
+          <t>132634</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>176097</t>
+          <t>178183</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>215295</t>
+          <t>215570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>270642</t>
+          <t>268442</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>56854</t>
+          <t>56803</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>87776</t>
+          <t>88085</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111561</t>
+          <t>112350</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>152418</t>
+          <t>152155</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>176964</t>
+          <t>177145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>228345</t>
+          <t>227748</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118185</t>
+          <t>117771</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>153931</t>
+          <t>154863</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>171419</t>
+          <t>171357</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>217340</t>
+          <t>220103</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>299576</t>
+          <t>301188</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>358537</t>
+          <t>360514</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26048</t>
+          <t>26133</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>50250</t>
+          <t>50952</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40503</t>
+          <t>40057</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>71241</t>
+          <t>69573</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>30996</t>
+          <t>30573</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>55222</t>
+          <t>54675</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39002</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>67466</t>
+          <t>66708</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>73891</t>
+          <t>75368</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>111664</t>
+          <t>111859</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>22714</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>44065</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>271890</t>
+          <t>272044</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>328815</t>
+          <t>334292</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>299293</t>
+          <t>301846</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>366004</t>
+          <t>366094</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>58490</t>
+          <t>59810</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>88099</t>
+          <t>89743</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>243907</t>
+          <t>248171</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>304608</t>
+          <t>305286</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>316055</t>
+          <t>318573</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>378779</t>
+          <t>380387</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>132717</t>
+          <t>135552</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>167993</t>
+          <t>168748</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>479241</t>
+          <t>479312</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>547655</t>
+          <t>547341</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>628454</t>
+          <t>626927</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>707928</t>
+          <t>703717</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>26948</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>40260</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>68128</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>53461</t>
+          <t>55342</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>87649</t>
+          <t>87489</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>33940</t>
+          <t>33305</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>85198</t>
+          <t>85018</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>122706</t>
+          <t>126179</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>106401</t>
+          <t>108368</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>150807</t>
+          <t>150517</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>672235</t>
+          <t>675074</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>771845</t>
+          <t>772518</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>767907</t>
+          <t>767381</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>868693</t>
+          <t>868038</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1473206</t>
+          <t>1477620</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1611563</t>
+          <t>1613035</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>769542</t>
+          <t>769507</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>866021</t>
+          <t>867221</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>758059</t>
+          <t>755485</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>859354</t>
+          <t>859704</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1554648</t>
+          <t>1557769</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1696945</t>
+          <t>1701354</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1226084</t>
+          <t>1227444</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1343172</t>
+          <t>1342345</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1248233</t>
+          <t>1250740</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1365813</t>
+          <t>1362413</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2517302</t>
+          <t>2519640</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2674391</t>
+          <t>2683987</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>143120</t>
+          <t>142378</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>194406</t>
+          <t>194514</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>159847</t>
+          <t>158729</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>214927</t>
+          <t>214117</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>314501</t>
+          <t>315952</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>386247</t>
+          <t>386556</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>245078</t>
+          <t>243253</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>307287</t>
+          <t>306949</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>228366</t>
+          <t>227790</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>287789</t>
+          <t>292670</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>483368</t>
+          <t>486332</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>575459</t>
+          <t>573406</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>143444</t>
+          <t>141508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>187131</t>
+          <t>185471</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97803</t>
+          <t>99053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133777</t>
+          <t>133744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248855</t>
+          <t>249957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>304791</t>
+          <t>305442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123914</t>
+          <t>121777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165409</t>
+          <t>162866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92818</t>
+          <t>93754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128339</t>
+          <t>128414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226040</t>
+          <t>227220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281214</t>
+          <t>281660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64940</t>
+          <t>65169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100170</t>
+          <t>99903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39366</t>
+          <t>39898</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67252</t>
+          <t>69029</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113389</t>
+          <t>113261</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>158504</t>
+          <t>158261</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22847</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39632</t>
+          <t>40355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>24240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50884</t>
+          <t>47982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39671</t>
+          <t>39623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71814</t>
+          <t>70799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105295</t>
+          <t>102679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144289</t>
+          <t>143710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98482</t>
+          <t>98629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137367</t>
+          <t>137104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>210174</t>
+          <t>213539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264459</t>
+          <t>268738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134047</t>
+          <t>135202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>176375</t>
+          <t>176515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95362</t>
+          <t>94331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130738</t>
+          <t>130188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239491</t>
+          <t>241320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296188</t>
+          <t>295285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75463</t>
+          <t>75078</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110651</t>
+          <t>111713</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>61054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91949</t>
+          <t>93393</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144766</t>
+          <t>143820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192924</t>
+          <t>192198</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22635</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>32912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>23819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49007</t>
+          <t>49339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>35593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44355</t>
+          <t>43991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75061</t>
+          <t>76209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>209344</t>
+          <t>211774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260912</t>
+          <t>262555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92425</t>
+          <t>93788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126810</t>
+          <t>126942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>316625</t>
+          <t>313911</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>374819</t>
+          <t>375527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177037</t>
+          <t>177610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>224230</t>
+          <t>223134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58154</t>
+          <t>59201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87472</t>
+          <t>88952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247284</t>
+          <t>243182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301325</t>
+          <t>298426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96368</t>
+          <t>94971</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134183</t>
+          <t>134903</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>29420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53825</t>
+          <t>52572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>132977</t>
+          <t>132477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176638</t>
+          <t>176874</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32012</t>
+          <t>29574</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51754</t>
+          <t>49149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85505</t>
+          <t>83279</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>20381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41122</t>
+          <t>41594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77568</t>
+          <t>78307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116040</t>
+          <t>117974</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>377806</t>
+          <t>379625</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>444382</t>
+          <t>446997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>255613</t>
+          <t>254485</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310470</t>
+          <t>309922</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>649188</t>
+          <t>650858</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>740222</t>
+          <t>737694</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>335781</t>
+          <t>339248</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>400649</t>
+          <t>404709</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>226610</t>
+          <t>226698</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>282025</t>
+          <t>280013</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>581484</t>
+          <t>578777</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>665010</t>
+          <t>671393</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>179711</t>
+          <t>177075</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>234620</t>
+          <t>229765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131946</t>
+          <t>130349</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>178260</t>
+          <t>176297</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>322681</t>
+          <t>321207</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>392246</t>
+          <t>392113</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33361</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61432</t>
+          <t>60462</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118001</t>
+          <t>115143</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>164936</t>
+          <t>162986</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51920</t>
+          <t>52088</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83882</t>
+          <t>85612</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>178913</t>
+          <t>178429</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>232425</t>
+          <t>233845</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>156053</t>
+          <t>154266</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>198205</t>
+          <t>196807</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>273551</t>
+          <t>270914</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>327235</t>
+          <t>325627</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>439549</t>
+          <t>435937</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>508318</t>
+          <t>510476</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>131348</t>
+          <t>130722</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>174430</t>
+          <t>173129</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>181693</t>
+          <t>180423</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>233388</t>
+          <t>231203</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>327790</t>
+          <t>325267</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>392191</t>
+          <t>391696</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73316</t>
+          <t>71195</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107853</t>
+          <t>106721</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>87006</t>
+          <t>86263</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>126660</t>
+          <t>129064</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>166123</t>
+          <t>167396</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>219591</t>
+          <t>221819</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29309</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>17785</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39213</t>
+          <t>39955</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>70355</t>
+          <t>71150</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>107311</t>
+          <t>104491</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>106992</t>
+          <t>107112</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>149289</t>
+          <t>148707</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>189028</t>
+          <t>189201</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>242878</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>58730</t>
+          <t>57489</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>88358</t>
+          <t>88624</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>470443</t>
+          <t>472894</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>535195</t>
+          <t>538391</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>541757</t>
+          <t>540327</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>616981</t>
+          <t>615111</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>89591</t>
+          <t>88305</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>119945</t>
+          <t>121002</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>277142</t>
+          <t>277634</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>337343</t>
+          <t>338793</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>377764</t>
+          <t>377995</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>446227</t>
+          <t>444857</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>47521</t>
+          <t>47350</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>73838</t>
+          <t>74010</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>151710</t>
+          <t>153822</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>201264</t>
+          <t>202104</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>211229</t>
+          <t>210529</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>266612</t>
+          <t>265867</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19860</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>40448</t>
+          <t>41061</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26812</t>
+          <t>26647</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50473</t>
+          <t>52084</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>31874</t>
+          <t>34209</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>71034</t>
+          <t>70424</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>106076</t>
+          <t>106821</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>85829</t>
+          <t>89002</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>127410</t>
+          <t>131192</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1122633</t>
+          <t>1123748</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1242160</t>
+          <t>1242483</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1367083</t>
+          <t>1367457</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1487064</t>
+          <t>1489754</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2513014</t>
+          <t>2520827</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2690393</t>
+          <t>2686502</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1070400</t>
+          <t>1060670</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1177267</t>
+          <t>1177801</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1003976</t>
+          <t>1007780</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1112458</t>
+          <t>1118581</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2103213</t>
+          <t>2100643</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2261242</t>
+          <t>2266159</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>596104</t>
+          <t>594528</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>690124</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>557358</t>
+          <t>555472</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>648582</t>
+          <t>646856</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1174756</t>
+          <t>1176991</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1303695</t>
+          <t>1305167</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>69903</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>107731</t>
+          <t>109519</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>74526</t>
+          <t>74691</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>114313</t>
+          <t>109997</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>154294</t>
+          <t>150973</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>208227</t>
+          <t>207352</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>343768</t>
+          <t>347424</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>425703</t>
+          <t>422827</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>321578</t>
+          <t>314186</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>394684</t>
+          <t>390245</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>687773</t>
+          <t>681746</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>793574</t>
+          <t>792171</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126638</t>
+          <t>126446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168281</t>
+          <t>167456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112088</t>
+          <t>111837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146960</t>
+          <t>148132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247902</t>
+          <t>248256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>302346</t>
+          <t>304093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143382</t>
+          <t>142978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186064</t>
+          <t>186373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119133</t>
+          <t>117719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>154891</t>
+          <t>154985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274944</t>
+          <t>272275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>329610</t>
+          <t>329614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59754</t>
+          <t>59568</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93067</t>
+          <t>92467</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>48027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76668</t>
+          <t>75007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115338</t>
+          <t>114201</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>157332</t>
+          <t>158463</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20806</t>
+          <t>19892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,82 +11102,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5783</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12570</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>17032</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>10034</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>27666</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5783</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12387</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>3,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>17032</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>10154</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>27256</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>20839</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45090</t>
+          <t>43606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33659</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61007</t>
+          <t>61036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120099</t>
+          <t>120262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159610</t>
+          <t>158957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105868</t>
+          <t>105715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143913</t>
+          <t>145151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235453</t>
+          <t>237212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286233</t>
+          <t>290482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>122701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162721</t>
+          <t>161618</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120144</t>
+          <t>120173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158433</t>
+          <t>158552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258237</t>
+          <t>256321</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309964</t>
+          <t>308504</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50574</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81063</t>
+          <t>79966</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57229</t>
+          <t>56290</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>87623</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115567</t>
+          <t>114689</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>159173</t>
+          <t>156645</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>17616</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>26750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16072</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37271</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30187</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26586</t>
+          <t>27761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52880</t>
+          <t>53858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160820</t>
+          <t>157001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202126</t>
+          <t>201476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47871</t>
+          <t>47639</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73062</t>
+          <t>74682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>215980</t>
+          <t>215971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266063</t>
+          <t>263590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170799</t>
+          <t>172239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>216401</t>
+          <t>218364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53244</t>
+          <t>52980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77910</t>
+          <t>79498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235004</t>
+          <t>235118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>284149</t>
+          <t>284606</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78102</t>
+          <t>78465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113485</t>
+          <t>113056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20345</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40344</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>105472</t>
+          <t>103921</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143486</t>
+          <t>141664</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19581</t>
+          <t>17950</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22382</t>
+          <t>22292</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>29072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54965</t>
+          <t>54626</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>35875</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62379</t>
+          <t>64288</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>352420</t>
+          <t>355164</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>415315</t>
+          <t>418912</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>229474</t>
+          <t>223365</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>280683</t>
+          <t>282517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>599455</t>
+          <t>595565</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>681091</t>
+          <t>679657</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>368649</t>
+          <t>369511</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>437291</t>
+          <t>433357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283487</t>
+          <t>284649</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339083</t>
+          <t>341061</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>671489</t>
+          <t>671434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>751845</t>
+          <t>758685</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194151</t>
+          <t>196543</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>248282</t>
+          <t>250650</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>156950</t>
+          <t>153552</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>202909</t>
+          <t>201751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>367108</t>
+          <t>365148</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>435896</t>
+          <t>437895</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38736</t>
+          <t>39636</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>28949</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34031</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61256</t>
+          <t>62048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90526</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128815</t>
+          <t>129650</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44768</t>
+          <t>45279</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>77030</t>
+          <t>76210</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>143812</t>
+          <t>145823</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>195478</t>
+          <t>193387</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>165817</t>
+          <t>165634</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>211548</t>
+          <t>210456</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>244837</t>
+          <t>242886</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>296936</t>
+          <t>297040</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>424722</t>
+          <t>422457</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>494089</t>
+          <t>492574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>191198</t>
+          <t>192134</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>237874</t>
+          <t>241901</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>231540</t>
+          <t>231012</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>283001</t>
+          <t>283077</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>436615</t>
+          <t>441393</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>507843</t>
+          <t>512875</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>95060</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>138116</t>
+          <t>135538</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>114399</t>
+          <t>111040</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>155467</t>
+          <t>153115</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>224114</t>
+          <t>222933</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>280505</t>
+          <t>281442</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30013</t>
+          <t>30881</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>41132</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>65896</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>98125</t>
+          <t>100720</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54721</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>87959</t>
+          <t>87573</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>128891</t>
+          <t>125813</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>176841</t>
+          <t>172540</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71595</t>
+          <t>68962</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>103079</t>
+          <t>101727</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>339501</t>
+          <t>343816</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>406607</t>
+          <t>408353</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>426021</t>
+          <t>426254</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>496648</t>
+          <t>504415</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>83614</t>
+          <t>83595</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>114861</t>
+          <t>115323</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>343559</t>
+          <t>345277</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>405007</t>
+          <t>410543</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>438454</t>
+          <t>439935</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>506982</t>
+          <t>512667</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>55898</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84339</t>
+          <t>84750</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>157168</t>
+          <t>155441</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>206716</t>
+          <t>205700</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>220404</t>
+          <t>222335</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>281259</t>
+          <t>280293</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26317</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>41269</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>28825</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>109349</t>
+          <t>110629</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>156267</t>
+          <t>154769</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>129943</t>
+          <t>128802</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>180089</t>
+          <t>178362</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1068920</t>
+          <t>1065897</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1176444</t>
+          <t>1180468</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1156137</t>
+          <t>1155070</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1276539</t>
+          <t>1273252</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2251359</t>
+          <t>2253256</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2417747</t>
+          <t>2406233</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1161035</t>
+          <t>1157401</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1276651</t>
+          <t>1274415</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1232823</t>
+          <t>1223901</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1341693</t>
+          <t>1339785</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2418013</t>
+          <t>2421068</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2581141</t>
+          <t>2575270</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>598284</t>
+          <t>599637</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>685740</t>
+          <t>688060</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>605972</t>
+          <t>603062</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>698472</t>
+          <t>700880</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1225053</t>
+          <t>1226417</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1360631</t>
+          <t>1352545</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>73547</t>
+          <t>74055</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>110450</t>
+          <t>113423</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>54807</t>
+          <t>54600</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>137707</t>
+          <t>136227</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>187047</t>
+          <t>186704</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>269409</t>
+          <t>267355</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>335794</t>
+          <t>334396</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>267491</t>
+          <t>270991</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>339714</t>
+          <t>339629</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>558003</t>
+          <t>558277</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>653886</t>
+          <t>653174</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
